--- a/data/AMS_DDS_Conventies.xlsx
+++ b/data/AMS_DDS_Conventies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://snbv-my.sharepoint.com/personal/arjen_rademaker_schiphol_nl/Documents/Bureaublad/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rademaker_A\OneDrive - Schiphol Nederland BV\Bureaublad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="458" documentId="8_{797709F9-9F51-4252-9A44-4503CF276D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85F159EC-3718-4B92-B948-9F17D56FD0F8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81265B35-B564-4D59-A0EC-601498FAD2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="86280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
   </bookViews>
   <sheets>
     <sheet name="Conventies" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="179">
   <si>
     <t>134^HNK</t>
   </si>
@@ -532,6 +532,48 @@
   </si>
   <si>
     <t>^HB\d{1,4}$</t>
+  </si>
+  <si>
+    <t>Brandblusser</t>
+  </si>
+  <si>
+    <t>Vluchtwegplattegrond</t>
+  </si>
+  <si>
+    <t>Brandslanghaspel</t>
+  </si>
+  <si>
+    <t>Blusmiddelen</t>
+  </si>
+  <si>
+    <t>BhvKast</t>
+  </si>
+  <si>
+    <t>EvacChair</t>
+  </si>
+  <si>
+    <t>^.+/[A-Za-z]+/\d+$</t>
+  </si>
+  <si>
+    <t>ter3/bb/129</t>
+  </si>
+  <si>
+    <t>[bouwdeel en verdieping]/[Afkorting asset]/[Volgnummer]</t>
+  </si>
+  <si>
+    <t>^.+$</t>
+  </si>
+  <si>
+    <t>^BSH\d+$</t>
+  </si>
+  <si>
+    <t>^BHV\d+$</t>
+  </si>
+  <si>
+    <t>BHV[Volgnummer]</t>
+  </si>
+  <si>
+    <t>BSH[Volgnummer]</t>
   </si>
 </sst>
 </file>
@@ -600,7 +642,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -665,8 +707,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}" name="Tabel1" displayName="Tabel1" ref="A1:I37" totalsRowShown="0">
-  <autoFilter ref="A1:I37" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}" name="Tabel1" displayName="Tabel1" ref="A1:I42" totalsRowShown="0">
+  <autoFilter ref="A1:I42" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{500614DB-F066-4803-9D7F-D1DF260731DF}" name="Assetgroep"/>
     <tableColumn id="6" xr3:uid="{B187B50A-9B2E-4EB0-AB39-0E7B1305F4A0}" name="IRI (o.b.v. DDS 3.5)"/>
@@ -683,7 +725,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -999,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA06F8D5-91AC-47C4-8305-7327008941AA}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -2071,6 +2113,118 @@
       </c>
       <c r="I37" s="3" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" t="s">
+        <v>165</v>
+      </c>
+      <c r="C38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40" t="s">
+        <v>167</v>
+      </c>
+      <c r="C40" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>168</v>
+      </c>
+      <c r="B41" t="s">
+        <v>169</v>
+      </c>
+      <c r="C41" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>168</v>
+      </c>
+      <c r="B42" t="s">
+        <v>170</v>
+      </c>
+      <c r="C42" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/data/AMS_DDS_Conventies.xlsx
+++ b/data/AMS_DDS_Conventies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rademaker_A\OneDrive - Schiphol Nederland BV\Bureaublad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81265B35-B564-4D59-A0EC-601498FAD2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
   </bookViews>
@@ -552,28 +552,28 @@
     <t>EvacChair</t>
   </si>
   <si>
-    <t>^.+/[A-Za-z]+/\d+$</t>
-  </si>
-  <si>
     <t>ter3/bb/129</t>
   </si>
   <si>
-    <t>[bouwdeel en verdieping]/[Afkorting asset]/[Volgnummer]</t>
-  </si>
-  <si>
     <t>^.+$</t>
   </si>
   <si>
-    <t>^BSH\d+$</t>
-  </si>
-  <si>
     <t>^BHV\d+$</t>
   </si>
   <si>
     <t>BHV[Volgnummer]</t>
   </si>
   <si>
-    <t>BSH[Volgnummer]</t>
+    <t>^.+/bb/\d+$</t>
+  </si>
+  <si>
+    <t>^.+/bsh/\d+$</t>
+  </si>
+  <si>
+    <t>[bouwdeel en verdieping]/bb/[Volgnummer]</t>
+  </si>
+  <si>
+    <t>[bouwdeel en verdieping]/bsh/[Volgnummer]</t>
   </si>
 </sst>
 </file>
@@ -2126,13 +2126,13 @@
         <v>104</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>145</v>
@@ -2152,7 +2152,7 @@
         <v>104</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>145</v>
@@ -2172,7 +2172,7 @@
         <v>104</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>178</v>
@@ -2195,10 +2195,10 @@
         <v>104</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>145</v>
@@ -2218,7 +2218,7 @@
         <v>104</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>145</v>

--- a/data/AMS_DDS_Conventies.xlsx
+++ b/data/AMS_DDS_Conventies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rademaker_A\OneDrive - Schiphol Nederland BV\Bureaublad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://snbv-my.sharepoint.com/personal/arjen_rademaker_schiphol_nl/Documents/Bureaublad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E3217F0-CAAB-407F-B710-8B8EDB23F3A4}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
+    <workbookView xWindow="86280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
   </bookViews>
   <sheets>
     <sheet name="Conventies" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="182">
   <si>
     <t>134^HNK</t>
   </si>
@@ -574,6 +574,15 @@
   </si>
   <si>
     <t>[bouwdeel en verdieping]/bsh/[Volgnummer]</t>
+  </si>
+  <si>
+    <t>Locatietoekenning</t>
+  </si>
+  <si>
+    <t>Ruimte</t>
+  </si>
+  <si>
+    <t>Verdieping</t>
   </si>
 </sst>
 </file>
@@ -644,7 +653,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -707,18 +724,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}" name="Tabel1" displayName="Tabel1" ref="A1:I42" totalsRowShown="0">
-  <autoFilter ref="A1:I42" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}" name="Tabel1" displayName="Tabel1" ref="A1:J42" totalsRowShown="0">
+  <autoFilter ref="A1:J42" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{500614DB-F066-4803-9D7F-D1DF260731DF}" name="Assetgroep"/>
     <tableColumn id="6" xr3:uid="{B187B50A-9B2E-4EB0-AB39-0E7B1305F4A0}" name="IRI (o.b.v. DDS 3.5)"/>
     <tableColumn id="9" xr3:uid="{B8AE657D-A708-4F28-84C6-AA8961A65712}" name="ObjectID benodigd?"/>
-    <tableColumn id="3" xr3:uid="{42DBBC0D-DB7E-42B7-9B77-EA00B6F0EF9F}" name="AasCode - Regular expression" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{8C12A5AD-4BA1-406F-9DC0-B27B7576E7E3}" name="AasCode - Opbouw" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{018765EF-F5D8-4DC5-A1EB-8C4B54B8A1EC}" name="AasCode - Voorbeeld" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{0BC790AE-DF3D-4129-9FF1-3C37576075EC}" name="Assetbeschrijving - Regular expression" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{F044C1AD-5182-459F-B1DE-A34E5BC6E030}" name="Assetbeschrijving - Opbouw" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{E31BBB01-9FF6-434A-8068-EF904FDB66B3}" name="Assetbeschrijving - Voorbeeld" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{42DBBC0D-DB7E-42B7-9B77-EA00B6F0EF9F}" name="AasCode - Regular expression" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{8C12A5AD-4BA1-406F-9DC0-B27B7576E7E3}" name="AasCode - Opbouw" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{018765EF-F5D8-4DC5-A1EB-8C4B54B8A1EC}" name="AasCode - Voorbeeld" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{0BC790AE-DF3D-4129-9FF1-3C37576075EC}" name="Assetbeschrijving - Regular expression" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{F044C1AD-5182-459F-B1DE-A34E5BC6E030}" name="Assetbeschrijving - Opbouw" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{E31BBB01-9FF6-434A-8068-EF904FDB66B3}" name="Assetbeschrijving - Voorbeeld" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{2E810100-F672-44A4-B4FA-D135617C4D9E}" name="Locatietoekenning" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1041,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA06F8D5-91AC-47C4-8305-7327008941AA}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1057,7 +1075,7 @@
     <col min="11" max="11" width="41.26171875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1085,8 +1103,11 @@
       <c r="I1" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1114,8 +1135,11 @@
       <c r="I2" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J2" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1140,8 +1164,11 @@
       <c r="I3" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="J3" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1166,8 +1193,11 @@
       <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J4" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -1195,8 +1225,11 @@
       <c r="I5" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J5" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1224,8 +1257,11 @@
       <c r="I6" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J6" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -1253,8 +1289,11 @@
       <c r="I7" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J7" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1282,8 +1321,11 @@
       <c r="I8" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J8" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -1311,8 +1353,11 @@
       <c r="I9" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J9" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -1340,8 +1385,11 @@
       <c r="I10" s="3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J10" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -1360,8 +1408,11 @@
       <c r="F11" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J11" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -1389,8 +1440,11 @@
       <c r="I12" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J12" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -1418,8 +1472,11 @@
       <c r="I13" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J13" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -1447,8 +1504,11 @@
       <c r="I14" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J14" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1476,8 +1536,11 @@
       <c r="I15" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J15" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1505,8 +1568,11 @@
       <c r="I16" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J16" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1534,8 +1600,11 @@
       <c r="I17" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J17" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1563,8 +1632,11 @@
       <c r="I18" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J18" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -1592,8 +1664,11 @@
       <c r="I19" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J19" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1621,8 +1696,11 @@
       <c r="I20" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J20" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -1650,8 +1728,11 @@
       <c r="I21" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J21" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1679,8 +1760,11 @@
       <c r="I22" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J22" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -1708,8 +1792,11 @@
       <c r="I23" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J23" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>140</v>
       </c>
@@ -1737,8 +1824,11 @@
       <c r="I24" s="3" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J24" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>140</v>
       </c>
@@ -1766,8 +1856,11 @@
       <c r="I25" s="3" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J25" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>140</v>
       </c>
@@ -1795,8 +1888,11 @@
       <c r="I26" s="3" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J26" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>140</v>
       </c>
@@ -1824,8 +1920,11 @@
       <c r="I27" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J27" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>140</v>
       </c>
@@ -1853,8 +1952,11 @@
       <c r="I28" s="3" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J28" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>140</v>
       </c>
@@ -1882,8 +1984,11 @@
       <c r="I29" s="3" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J29" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>140</v>
       </c>
@@ -1911,8 +2016,11 @@
       <c r="I30" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J30" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>140</v>
       </c>
@@ -1940,8 +2048,11 @@
       <c r="I31" s="3" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J31" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>140</v>
       </c>
@@ -1969,8 +2080,11 @@
       <c r="I32" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J32" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>140</v>
       </c>
@@ -1998,8 +2112,11 @@
       <c r="I33" s="3" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J33" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>140</v>
       </c>
@@ -2027,8 +2144,11 @@
       <c r="I34" s="3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J34" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>140</v>
       </c>
@@ -2056,8 +2176,11 @@
       <c r="I35" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J35" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>140</v>
       </c>
@@ -2085,8 +2208,11 @@
       <c r="I36" s="3" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J36" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>140</v>
       </c>
@@ -2114,8 +2240,11 @@
       <c r="I37" s="3" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J37" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>168</v>
       </c>
@@ -2140,8 +2269,11 @@
       <c r="H38" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J38" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>168</v>
       </c>
@@ -2160,8 +2292,11 @@
       <c r="H39" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J39" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>168</v>
       </c>
@@ -2183,8 +2318,11 @@
       <c r="H40" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J40" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>168</v>
       </c>
@@ -2206,8 +2344,11 @@
       <c r="H41" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J41" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>168</v>
       </c>
@@ -2225,6 +2366,9 @@
       </c>
       <c r="H42" s="3" t="s">
         <v>146</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/data/AMS_DDS_Conventies.xlsx
+++ b/data/AMS_DDS_Conventies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://snbv-my.sharepoint.com/personal/arjen_rademaker_schiphol_nl/Documents/Bureaublad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E3217F0-CAAB-407F-B710-8B8EDB23F3A4}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6333E61C-8AD3-4E15-B97E-B5CD49CA371E}"/>
   <bookViews>
     <workbookView xWindow="86280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
   </bookViews>
@@ -1633,7 +1633,7 @@
         <v>67</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">

--- a/data/AMS_DDS_Conventies.xlsx
+++ b/data/AMS_DDS_Conventies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://snbv-my.sharepoint.com/personal/arjen_rademaker_schiphol_nl/Documents/Bureaublad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6333E61C-8AD3-4E15-B97E-B5CD49CA371E}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3769FDD5-5381-4691-B264-BFDA2E93D4DF}"/>
   <bookViews>
     <workbookView xWindow="86280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
   </bookViews>
@@ -1569,7 +1569,7 @@
         <v>61</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1601,7 +1601,7 @@
         <v>68</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">

--- a/data/AMS_DDS_Conventies.xlsx
+++ b/data/AMS_DDS_Conventies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://snbv-my.sharepoint.com/personal/arjen_rademaker_schiphol_nl/Documents/Bureaublad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3769FDD5-5381-4691-B264-BFDA2E93D4DF}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3076946-9FB0-43F5-B040-A20E03716960}"/>
   <bookViews>
     <workbookView xWindow="86280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
   </bookViews>
@@ -1569,7 +1569,7 @@
         <v>61</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1601,7 +1601,7 @@
         <v>68</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1633,7 +1633,7 @@
         <v>67</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1665,7 +1665,7 @@
         <v>66</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1793,7 +1793,7 @@
         <v>62</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">

--- a/data/AMS_DDS_Conventies.xlsx
+++ b/data/AMS_DDS_Conventies.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://snbv-my.sharepoint.com/personal/arjen_rademaker_schiphol_nl/Documents/Bureaublad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3076946-9FB0-43F5-B040-A20E03716960}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B1477D-4428-4EDD-8D1E-0BF55D3BFBEC}"/>
   <bookViews>
-    <workbookView xWindow="86280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="2" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
   </bookViews>
   <sheets>
     <sheet name="Conventies" sheetId="1" r:id="rId1"/>
-    <sheet name="Versie toetsingsregel" sheetId="3" r:id="rId2"/>
+    <sheet name="Picklist" sheetId="4" state="hidden" r:id="rId2"/>
+    <sheet name="Versie toetsingsregel" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="182">
   <si>
     <t>134^HNK</t>
   </si>
@@ -339,9 +340,6 @@
     <t>Datum</t>
   </si>
   <si>
-    <t>0.82</t>
-  </si>
-  <si>
     <t>[1,2 of 3-cijfers]^HNK</t>
   </si>
   <si>
@@ -583,6 +581,9 @@
   </si>
   <si>
     <t>Verdieping</t>
+  </si>
+  <si>
+    <t>Gebouw</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1072,7 @@
     <col min="7" max="7" width="37.26171875" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="55.68359375" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="70.83984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="81.26171875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.3125" customWidth="1"/>
     <col min="11" max="11" width="41.26171875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1083,10 +1084,10 @@
         <v>73</v>
       </c>
       <c r="C1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>97</v>
@@ -1104,7 +1105,7 @@
         <v>12</v>
       </c>
       <c r="J1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1115,13 +1116,13 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
@@ -1136,7 +1137,7 @@
         <v>56</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1147,7 +1148,7 @@
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>9</v>
@@ -1165,7 +1166,7 @@
         <v>57</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1176,10 +1177,10 @@
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>2</v>
@@ -1194,7 +1195,7 @@
         <v>58</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1205,13 +1206,13 @@
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>3</v>
@@ -1226,7 +1227,7 @@
         <v>59</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1237,13 +1238,13 @@
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>4</v>
@@ -1258,7 +1259,7 @@
         <v>14</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1269,13 +1270,13 @@
         <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -1290,7 +1291,7 @@
         <v>15</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1301,13 +1302,13 @@
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
@@ -1322,7 +1323,7 @@
         <v>16</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1333,13 +1334,13 @@
         <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>7</v>
@@ -1354,7 +1355,7 @@
         <v>60</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1365,13 +1366,13 @@
         <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>8</v>
@@ -1383,10 +1384,10 @@
         <v>55</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1397,19 +1398,19 @@
         <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1420,13 +1421,13 @@
         <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>26</v>
@@ -1452,13 +1453,13 @@
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>27</v>
@@ -1473,7 +1474,7 @@
         <v>71</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1484,13 +1485,13 @@
         <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>28</v>
@@ -1505,7 +1506,7 @@
         <v>69</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1516,13 +1517,13 @@
         <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>28</v>
@@ -1537,7 +1538,7 @@
         <v>70</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1548,13 +1549,13 @@
         <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>29</v>
@@ -1569,7 +1570,7 @@
         <v>61</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1580,13 +1581,13 @@
         <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>36</v>
@@ -1601,7 +1602,7 @@
         <v>68</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1612,13 +1613,13 @@
         <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>30</v>
@@ -1633,7 +1634,7 @@
         <v>67</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1644,13 +1645,13 @@
         <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>37</v>
@@ -1665,7 +1666,7 @@
         <v>66</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1676,13 +1677,13 @@
         <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>74</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>38</v>
@@ -1697,7 +1698,7 @@
         <v>65</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1708,13 +1709,13 @@
         <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>32</v>
@@ -1729,7 +1730,7 @@
         <v>64</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1740,13 +1741,13 @@
         <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>31</v>
@@ -1761,7 +1762,7 @@
         <v>63</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1772,13 +1773,13 @@
         <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>37</v>
@@ -1793,582 +1794,582 @@
         <v>62</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" t="s">
         <v>140</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C24" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G24" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I25" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I26" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I27" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I28" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I29" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I30" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I31" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="G32" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I32" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I33" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I34" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="H35" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I35" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="G36" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="H36" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I36" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="G37" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I37" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G38" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="J38" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G39" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G40" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41" t="s">
         <v>168</v>
       </c>
-      <c r="B41" t="s">
-        <v>169</v>
-      </c>
       <c r="C41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="G41" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="J41" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G42" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2376,10 +2377,47 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5DAA2793-62F4-4DF9-9477-FB1FBEDA3CD2}">
+          <x14:formula1>
+            <xm:f>Picklist!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>J1:J1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73FB73-6477-4FDB-8EEC-856BE0C24727}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{749A44F2-34BF-4A35-9B03-0840393CC5C7}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -2392,8 +2430,8 @@
       <c r="A1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" t="s">
-        <v>100</v>
+      <c r="B1">
+        <v>0.9</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -2401,7 +2439,7 @@
         <v>99</v>
       </c>
       <c r="B2" s="5">
-        <v>46080</v>
+        <v>46117</v>
       </c>
     </row>
   </sheetData>

--- a/data/AMS_DDS_Conventies.xlsx
+++ b/data/AMS_DDS_Conventies.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://snbv-my.sharepoint.com/personal/arjen_rademaker_schiphol_nl/Documents/Bureaublad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B1477D-4428-4EDD-8D1E-0BF55D3BFBEC}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DA6718A-1E22-45A9-8B85-963B970BCDA9}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="2" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
+    <workbookView xWindow="86280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
   </bookViews>
   <sheets>
     <sheet name="Conventies" sheetId="1" r:id="rId1"/>
-    <sheet name="Picklist" sheetId="4" state="hidden" r:id="rId2"/>
+    <sheet name="Picklist" sheetId="4" r:id="rId2"/>
     <sheet name="Versie toetsingsregel" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="183">
   <si>
     <t>134^HNK</t>
   </si>
@@ -584,6 +584,9 @@
   </si>
   <si>
     <t>Gebouw</t>
+  </si>
+  <si>
+    <t>Locatietoekenning - Montage in wand</t>
   </si>
 </sst>
 </file>
@@ -654,7 +657,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -725,19 +736,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}" name="Tabel1" displayName="Tabel1" ref="A1:J42" totalsRowShown="0">
-  <autoFilter ref="A1:J42" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}" name="Tabel1" displayName="Tabel1" ref="A1:K42" totalsRowShown="0">
+  <autoFilter ref="A1:K42" xr:uid="{8BE26161-F795-4918-987F-8C9B910BE80A}"/>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{500614DB-F066-4803-9D7F-D1DF260731DF}" name="Assetgroep"/>
     <tableColumn id="6" xr3:uid="{B187B50A-9B2E-4EB0-AB39-0E7B1305F4A0}" name="IRI (o.b.v. DDS 3.5)"/>
     <tableColumn id="9" xr3:uid="{B8AE657D-A708-4F28-84C6-AA8961A65712}" name="ObjectID benodigd?"/>
-    <tableColumn id="3" xr3:uid="{42DBBC0D-DB7E-42B7-9B77-EA00B6F0EF9F}" name="AasCode - Regular expression" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{8C12A5AD-4BA1-406F-9DC0-B27B7576E7E3}" name="AasCode - Opbouw" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{018765EF-F5D8-4DC5-A1EB-8C4B54B8A1EC}" name="AasCode - Voorbeeld" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{0BC790AE-DF3D-4129-9FF1-3C37576075EC}" name="Assetbeschrijving - Regular expression" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{F044C1AD-5182-459F-B1DE-A34E5BC6E030}" name="Assetbeschrijving - Opbouw" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{E31BBB01-9FF6-434A-8068-EF904FDB66B3}" name="Assetbeschrijving - Voorbeeld" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{2E810100-F672-44A4-B4FA-D135617C4D9E}" name="Locatietoekenning" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{42DBBC0D-DB7E-42B7-9B77-EA00B6F0EF9F}" name="AasCode - Regular expression" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{8C12A5AD-4BA1-406F-9DC0-B27B7576E7E3}" name="AasCode - Opbouw" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{018765EF-F5D8-4DC5-A1EB-8C4B54B8A1EC}" name="AasCode - Voorbeeld" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{0BC790AE-DF3D-4129-9FF1-3C37576075EC}" name="Assetbeschrijving - Regular expression" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{F044C1AD-5182-459F-B1DE-A34E5BC6E030}" name="Assetbeschrijving - Opbouw" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{E31BBB01-9FF6-434A-8068-EF904FDB66B3}" name="Assetbeschrijving - Voorbeeld" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{2E810100-F672-44A4-B4FA-D135617C4D9E}" name="Locatietoekenning" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{02F56C08-8D50-4710-9CDE-CA65A1A98689}" name="Locatietoekenning - Montage in wand" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1060,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA06F8D5-91AC-47C4-8305-7327008941AA}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1076,7 +1088,7 @@
     <col min="11" max="11" width="41.26171875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1107,8 +1119,11 @@
       <c r="J1" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1139,8 +1154,9 @@
       <c r="J2" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1168,8 +1184,9 @@
       <c r="J3" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1197,8 +1214,9 @@
       <c r="J4" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -1229,8 +1247,9 @@
       <c r="J5" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1261,8 +1280,9 @@
       <c r="J6" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -1293,8 +1313,9 @@
       <c r="J7" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1325,8 +1346,9 @@
       <c r="J8" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -1357,8 +1379,9 @@
       <c r="J9" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -1389,8 +1412,9 @@
       <c r="J10" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -1412,8 +1436,9 @@
       <c r="J11" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -1444,8 +1469,9 @@
       <c r="J12" s="3" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -1476,8 +1502,9 @@
       <c r="J13" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -1508,8 +1535,9 @@
       <c r="J14" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1540,8 +1568,9 @@
       <c r="J15" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1572,8 +1601,9 @@
       <c r="J16" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1604,8 +1634,9 @@
       <c r="J17" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1636,8 +1667,9 @@
       <c r="J18" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -1668,8 +1700,9 @@
       <c r="J19" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K19" s="3"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1700,8 +1733,9 @@
       <c r="J20" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -1732,8 +1766,9 @@
       <c r="J21" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1764,8 +1799,9 @@
       <c r="J22" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -1796,8 +1832,9 @@
       <c r="J23" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>139</v>
       </c>
@@ -1828,8 +1865,9 @@
       <c r="J24" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>139</v>
       </c>
@@ -1860,8 +1898,9 @@
       <c r="J25" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>139</v>
       </c>
@@ -1892,8 +1931,9 @@
       <c r="J26" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>139</v>
       </c>
@@ -1924,8 +1964,9 @@
       <c r="J27" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>139</v>
       </c>
@@ -1956,8 +1997,9 @@
       <c r="J28" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>139</v>
       </c>
@@ -1988,8 +2030,9 @@
       <c r="J29" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>139</v>
       </c>
@@ -2020,8 +2063,9 @@
       <c r="J30" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>139</v>
       </c>
@@ -2052,8 +2096,9 @@
       <c r="J31" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K31" s="3"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -2084,8 +2129,9 @@
       <c r="J32" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K32" s="3"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>139</v>
       </c>
@@ -2116,8 +2162,9 @@
       <c r="J33" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K33" s="3"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>139</v>
       </c>
@@ -2148,8 +2195,9 @@
       <c r="J34" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K34" s="3"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>139</v>
       </c>
@@ -2180,8 +2228,9 @@
       <c r="J35" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K35" s="3"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>139</v>
       </c>
@@ -2212,8 +2261,9 @@
       <c r="J36" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K36" s="3"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>139</v>
       </c>
@@ -2244,8 +2294,9 @@
       <c r="J37" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K37" s="3"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>167</v>
       </c>
@@ -2273,8 +2324,9 @@
       <c r="J38" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K38" s="3"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>167</v>
       </c>
@@ -2296,8 +2348,9 @@
       <c r="J39" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K39" s="3"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>167</v>
       </c>
@@ -2322,8 +2375,11 @@
       <c r="J40" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K40" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>167</v>
       </c>
@@ -2348,8 +2404,11 @@
       <c r="J41" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K41" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>167</v>
       </c>
@@ -2371,6 +2430,7 @@
       <c r="J42" s="3" t="s">
         <v>179</v>
       </c>
+      <c r="K42" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2379,12 +2439,18 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5DAA2793-62F4-4DF9-9477-FB1FBEDA3CD2}">
           <x14:formula1>
             <xm:f>Picklist!$A:$A</xm:f>
           </x14:formula1>
           <xm:sqref>J1:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E592FECF-CFFB-4B1F-BAF8-C09D562751EC}">
+          <x14:formula1>
+            <xm:f>Picklist!$C:$C</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2394,20 +2460,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73FB73-6477-4FDB-8EEC-856BE0C24727}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>181</v>
       </c>

--- a/data/AMS_DDS_Conventies.xlsx
+++ b/data/AMS_DDS_Conventies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://snbv-my.sharepoint.com/personal/arjen_rademaker_schiphol_nl/Documents/Bureaublad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DA6718A-1E22-45A9-8B85-963B970BCDA9}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{2CD5E73A-BED4-4AEB-A149-77B7EB539C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{356BD26F-C80D-4D94-8A02-2A8A6CCCAEA2}"/>
   <bookViews>
-    <workbookView xWindow="86280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2D98358A-0058-41E3-9878-D5F4C4F5CB06}"/>
   </bookViews>
   <sheets>
     <sheet name="Conventies" sheetId="1" r:id="rId1"/>
@@ -472,9 +472,6 @@
     <t>B1063</t>
   </si>
   <si>
-    <t>^[A-Za-z0-9 -]+,[[aascode]],.*</t>
-  </si>
-  <si>
     <t>[IRI], [AasCode], [Ruimtenummer]</t>
   </si>
   <si>
@@ -587,6 +584,9 @@
   </si>
   <si>
     <t>Locatietoekenning - Montage in wand</t>
+  </si>
+  <si>
+    <t>^[A-Za-z0-9 -]+, [[aascode]],.*</t>
   </si>
 </sst>
 </file>
@@ -1117,10 +1117,10 @@
         <v>12</v>
       </c>
       <c r="J1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -1152,7 +1152,7 @@
         <v>56</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K2" s="3"/>
     </row>
@@ -1182,7 +1182,7 @@
         <v>57</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K3" s="3"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>58</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K4" s="3"/>
     </row>
@@ -1227,7 +1227,7 @@
         <v>103</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>123</v>
@@ -1245,7 +1245,7 @@
         <v>59</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -1260,7 +1260,7 @@
         <v>103</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>119</v>
@@ -1278,7 +1278,7 @@
         <v>14</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K6" s="3"/>
     </row>
@@ -1293,7 +1293,7 @@
         <v>103</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>122</v>
@@ -1311,7 +1311,7 @@
         <v>15</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K7" s="3"/>
     </row>
@@ -1326,7 +1326,7 @@
         <v>103</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>121</v>
@@ -1344,7 +1344,7 @@
         <v>16</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K8" s="3"/>
     </row>
@@ -1377,7 +1377,7 @@
         <v>60</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K9" s="3"/>
     </row>
@@ -1392,7 +1392,7 @@
         <v>103</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>124</v>
@@ -1410,7 +1410,7 @@
         <v>125</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K10" s="3"/>
     </row>
@@ -1434,7 +1434,7 @@
         <v>33</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K11" s="3"/>
     </row>
@@ -1467,7 +1467,7 @@
         <v>72</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K12" s="3"/>
     </row>
@@ -1500,7 +1500,7 @@
         <v>71</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K13" s="3"/>
     </row>
@@ -1533,7 +1533,7 @@
         <v>69</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K14" s="3"/>
     </row>
@@ -1566,7 +1566,7 @@
         <v>70</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K15" s="3"/>
     </row>
@@ -1599,7 +1599,7 @@
         <v>61</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K16" s="3"/>
     </row>
@@ -1632,7 +1632,7 @@
         <v>68</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K17" s="3"/>
     </row>
@@ -1665,7 +1665,7 @@
         <v>67</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K18" s="3"/>
     </row>
@@ -1698,7 +1698,7 @@
         <v>66</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K19" s="3"/>
     </row>
@@ -1731,7 +1731,7 @@
         <v>65</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K20" s="3"/>
     </row>
@@ -1764,7 +1764,7 @@
         <v>64</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K21" s="3"/>
     </row>
@@ -1797,7 +1797,7 @@
         <v>63</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K22" s="3"/>
     </row>
@@ -1830,7 +1830,7 @@
         <v>62</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K23" s="3"/>
     </row>
@@ -1854,16 +1854,16 @@
         <v>143</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K24" s="3"/>
     </row>
@@ -1887,16 +1887,16 @@
         <v>143</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I25" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K25" s="3"/>
     </row>
@@ -1920,16 +1920,16 @@
         <v>143</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I26" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K26" s="3"/>
     </row>
@@ -1953,16 +1953,16 @@
         <v>143</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I27" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K27" s="3"/>
     </row>
@@ -1986,16 +1986,16 @@
         <v>143</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I28" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K28" s="3"/>
     </row>
@@ -2019,16 +2019,16 @@
         <v>143</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I29" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K29" s="3"/>
     </row>
@@ -2052,16 +2052,16 @@
         <v>143</v>
       </c>
       <c r="G30" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I30" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K30" s="3"/>
     </row>
@@ -2085,16 +2085,16 @@
         <v>143</v>
       </c>
       <c r="G31" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I31" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K31" s="3"/>
     </row>
@@ -2118,16 +2118,16 @@
         <v>143</v>
       </c>
       <c r="G32" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I32" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K32" s="3"/>
     </row>
@@ -2151,16 +2151,16 @@
         <v>143</v>
       </c>
       <c r="G33" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I33" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K33" s="3"/>
     </row>
@@ -2184,16 +2184,16 @@
         <v>143</v>
       </c>
       <c r="G34" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I34" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K34" s="3"/>
     </row>
@@ -2217,16 +2217,16 @@
         <v>143</v>
       </c>
       <c r="G35" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I35" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K35" s="3"/>
     </row>
@@ -2250,16 +2250,16 @@
         <v>143</v>
       </c>
       <c r="G36" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I36" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K36" s="3"/>
     </row>
@@ -2283,97 +2283,97 @@
         <v>143</v>
       </c>
       <c r="G37" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="I37" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K37" s="3"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G38" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="J38" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K38" s="3"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C39" t="s">
         <v>103</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G39" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K39" s="3"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C40" t="s">
         <v>103</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G40" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>103</v>
@@ -2381,28 +2381,28 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
+        <v>166</v>
+      </c>
+      <c r="B41" t="s">
         <v>167</v>
       </c>
-      <c r="B41" t="s">
-        <v>168</v>
-      </c>
       <c r="C41" t="s">
         <v>103</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="G41" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="J41" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>103</v>
@@ -2410,25 +2410,25 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C42" t="s">
         <v>103</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G42" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K42" s="3"/>
     </row>
@@ -2465,7 +2465,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C1" t="s">
         <v>103</v>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
         <v>104</v>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
